--- a/backend/data/financials_by_company/0707.HK.xlsx
+++ b/backend/data/financials_by_company/0707.HK.xlsx
@@ -662,586 +662,586 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-2990.183072</v>
+        <v>-23442191.4304</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000265</v>
+        <v>0.09704400000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>-77444000</v>
+        <v>-81104000</v>
       </c>
       <c r="E2" t="n">
-        <v>-11270000</v>
+        <v>-222589000</v>
       </c>
       <c r="F2" t="n">
-        <v>-11270000</v>
+        <v>-241562000</v>
       </c>
       <c r="G2" t="n">
-        <v>-120100000</v>
+        <v>-260665000</v>
       </c>
       <c r="H2" t="n">
-        <v>2320000</v>
+        <v>26304000</v>
       </c>
       <c r="I2" t="n">
-        <v>107826000</v>
+        <v>162450000</v>
       </c>
       <c r="J2" t="n">
-        <v>-88714000</v>
+        <v>-303693000</v>
       </c>
       <c r="K2" t="n">
-        <v>-91034000</v>
+        <v>-329997000</v>
       </c>
       <c r="L2" t="n">
-        <v>-54809000</v>
+        <v>-78139000</v>
       </c>
       <c r="M2" t="n">
-        <v>52188000</v>
+        <v>76323000</v>
       </c>
       <c r="N2" t="n">
-        <v>4000</v>
+        <v>192000</v>
       </c>
       <c r="O2" t="n">
-        <v>-108832990.183072</v>
+        <v>-23572191.4304</v>
       </c>
       <c r="P2" t="n">
-        <v>-120100000</v>
+        <v>-260665000</v>
       </c>
       <c r="Q2" t="n">
-        <v>158514000</v>
+        <v>247606000</v>
       </c>
       <c r="R2" t="n">
-        <v>1966618000</v>
+        <v>1045740021</v>
       </c>
       <c r="S2" t="n">
-        <v>1966618000</v>
+        <v>1045740021</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.249627</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.249627</v>
       </c>
       <c r="V2" t="n">
-        <v>-120100000</v>
+        <v>-260665000</v>
       </c>
       <c r="W2" t="n">
-        <v>-120100000</v>
+        <v>-260665000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-120100000</v>
+        <v>-260665000</v>
       </c>
       <c r="Z2" t="n">
-        <v>23084000</v>
+        <v>106224000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-143184000</v>
+        <v>-366889000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-143184000</v>
+        <v>-366889000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-38000</v>
+        <v>-39431000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-143222000</v>
+        <v>-406320000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1288000</v>
+        <v>2081000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-13156000</v>
+        <v>-195548000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1908000</v>
+        <v>-80639000</v>
       </c>
       <c r="AH2" t="n">
-        <v>10953000</v>
+        <v>10889000</v>
       </c>
       <c r="AI2" t="n">
-        <v>4111000</v>
+        <v>246325000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-54809000</v>
+        <v>-78139000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2625000</v>
+        <v>2008000</v>
       </c>
       <c r="AL2" t="n">
-        <v>52188000</v>
+        <v>76323000</v>
       </c>
       <c r="AM2" t="n">
-        <v>4000</v>
+        <v>192000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-78973000</v>
+        <v>-88742000</v>
       </c>
       <c r="AO2" t="n">
-        <v>50688000</v>
+        <v>85156000</v>
       </c>
       <c r="AP2" t="n">
-        <v>55853000</v>
+        <v>86015000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6343000</v>
+        <v>3698000</v>
       </c>
       <c r="AR2" t="n">
-        <v>49510000</v>
+        <v>82317000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-28285000</v>
+        <v>-3586000</v>
       </c>
       <c r="AT2" t="n">
-        <v>107826000</v>
+        <v>162450000</v>
       </c>
       <c r="AU2" t="n">
-        <v>79541000</v>
+        <v>158864000</v>
       </c>
       <c r="AV2" t="n">
-        <v>79541000</v>
+        <v>158864000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-31430.25042</v>
+        <v>-1455817.017367</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008295</v>
+        <v>0.030207</v>
       </c>
       <c r="D3" t="n">
-        <v>-77811000</v>
+        <v>-75803000</v>
       </c>
       <c r="E3" t="n">
-        <v>-3789000</v>
+        <v>-48194000</v>
       </c>
       <c r="F3" t="n">
-        <v>-3789000</v>
+        <v>-48194000</v>
       </c>
       <c r="G3" t="n">
-        <v>-132383000</v>
+        <v>-184415000</v>
       </c>
       <c r="H3" t="n">
-        <v>16646000</v>
+        <v>20934000</v>
       </c>
       <c r="I3" t="n">
-        <v>127840000</v>
+        <v>102696000</v>
       </c>
       <c r="J3" t="n">
-        <v>-81600000</v>
+        <v>-123997000</v>
       </c>
       <c r="K3" t="n">
-        <v>-98246000</v>
+        <v>-144931000</v>
       </c>
       <c r="L3" t="n">
-        <v>-70838000</v>
+        <v>-77182000</v>
       </c>
       <c r="M3" t="n">
-        <v>67755000</v>
+        <v>76008000</v>
       </c>
       <c r="N3" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="O3" t="n">
-        <v>-128625430.25042</v>
+        <v>-137676817.017367</v>
       </c>
       <c r="P3" t="n">
-        <v>-132383000</v>
+        <v>-184415000</v>
       </c>
       <c r="Q3" t="n">
-        <v>192578000</v>
+        <v>170960000</v>
       </c>
       <c r="R3" t="n">
-        <v>1151097375</v>
+        <v>1073161535</v>
       </c>
       <c r="S3" t="n">
-        <v>1151097375</v>
+        <v>1073161535</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.115037</v>
+        <v>-0.171797</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.115037</v>
+        <v>-0.171797</v>
       </c>
       <c r="V3" t="n">
-        <v>-132383000</v>
+        <v>-184415000</v>
       </c>
       <c r="W3" t="n">
-        <v>-132383000</v>
+        <v>-184415000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-132383000</v>
+        <v>-184415000</v>
       </c>
       <c r="Z3" t="n">
-        <v>32241000</v>
+        <v>29850000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-164624000</v>
+        <v>-214265000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-164624000</v>
+        <v>-214265000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1377000</v>
+        <v>-6674000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-166001000</v>
+        <v>-220939000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2253000</v>
+        <v>-1439000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-8540000</v>
+        <v>-26738000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-21823000</v>
+        <v>-27000000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2984000</v>
+        <v>-11239000</v>
       </c>
       <c r="AI3" t="n">
-        <v>27379000</v>
+        <v>64977000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-70838000</v>
+        <v>-77182000</v>
       </c>
       <c r="AK3" t="n">
-        <v>3091000</v>
+        <v>1178000</v>
       </c>
       <c r="AL3" t="n">
-        <v>67755000</v>
+        <v>76008000</v>
       </c>
       <c r="AM3" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-87269000</v>
+        <v>-93870000</v>
       </c>
       <c r="AO3" t="n">
-        <v>64738000</v>
+        <v>68264000</v>
       </c>
       <c r="AP3" t="n">
-        <v>64738000</v>
+        <v>69008000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6995000</v>
+        <v>1525000</v>
       </c>
       <c r="AR3" t="n">
-        <v>57743000</v>
+        <v>67483000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-22531000</v>
+        <v>-25606000</v>
       </c>
       <c r="AT3" t="n">
-        <v>127840000</v>
+        <v>102696000</v>
       </c>
       <c r="AU3" t="n">
-        <v>105309000</v>
+        <v>77090000</v>
       </c>
       <c r="AV3" t="n">
-        <v>105309000</v>
+        <v>77090000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1455817.017367</v>
+        <v>-31430.25042</v>
       </c>
       <c r="C4" t="n">
-        <v>0.030207</v>
+        <v>0.008295</v>
       </c>
       <c r="D4" t="n">
-        <v>-75803000</v>
+        <v>-77811000</v>
       </c>
       <c r="E4" t="n">
-        <v>-48194000</v>
+        <v>-3789000</v>
       </c>
       <c r="F4" t="n">
-        <v>-48194000</v>
+        <v>-3789000</v>
       </c>
       <c r="G4" t="n">
-        <v>-184415000</v>
+        <v>-132383000</v>
       </c>
       <c r="H4" t="n">
-        <v>20934000</v>
+        <v>16646000</v>
       </c>
       <c r="I4" t="n">
-        <v>102696000</v>
+        <v>127840000</v>
       </c>
       <c r="J4" t="n">
-        <v>-123997000</v>
+        <v>-81600000</v>
       </c>
       <c r="K4" t="n">
-        <v>-144931000</v>
+        <v>-98246000</v>
       </c>
       <c r="L4" t="n">
-        <v>-77182000</v>
+        <v>-70838000</v>
       </c>
       <c r="M4" t="n">
-        <v>76008000</v>
+        <v>67755000</v>
       </c>
       <c r="N4" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="O4" t="n">
-        <v>-137676817.017367</v>
+        <v>-128625430.25042</v>
       </c>
       <c r="P4" t="n">
-        <v>-184415000</v>
+        <v>-132383000</v>
       </c>
       <c r="Q4" t="n">
-        <v>170960000</v>
+        <v>192578000</v>
       </c>
       <c r="R4" t="n">
-        <v>1073161535</v>
+        <v>1151097375</v>
       </c>
       <c r="S4" t="n">
-        <v>1073161535</v>
+        <v>1151097375</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.171797</v>
+        <v>-0.115037</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.171797</v>
+        <v>-0.115037</v>
       </c>
       <c r="V4" t="n">
-        <v>-184415000</v>
+        <v>-132383000</v>
       </c>
       <c r="W4" t="n">
-        <v>-184415000</v>
+        <v>-132383000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-184415000</v>
+        <v>-132383000</v>
       </c>
       <c r="Z4" t="n">
-        <v>29850000</v>
+        <v>32241000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-214265000</v>
+        <v>-164624000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-214265000</v>
+        <v>-164624000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-6674000</v>
+        <v>-1377000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-220939000</v>
+        <v>-166001000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1439000</v>
+        <v>2253000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-26738000</v>
+        <v>-8540000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-27000000</v>
+        <v>-21823000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-11239000</v>
+        <v>2984000</v>
       </c>
       <c r="AI4" t="n">
-        <v>64977000</v>
+        <v>27379000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-77182000</v>
+        <v>-70838000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1178000</v>
+        <v>3091000</v>
       </c>
       <c r="AL4" t="n">
-        <v>76008000</v>
+        <v>67755000</v>
       </c>
       <c r="AM4" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-93870000</v>
+        <v>-87269000</v>
       </c>
       <c r="AO4" t="n">
-        <v>68264000</v>
+        <v>64738000</v>
       </c>
       <c r="AP4" t="n">
-        <v>69008000</v>
+        <v>64738000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1525000</v>
+        <v>6995000</v>
       </c>
       <c r="AR4" t="n">
-        <v>67483000</v>
+        <v>57743000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-25606000</v>
+        <v>-22531000</v>
       </c>
       <c r="AT4" t="n">
-        <v>102696000</v>
+        <v>127840000</v>
       </c>
       <c r="AU4" t="n">
-        <v>77090000</v>
+        <v>105309000</v>
       </c>
       <c r="AV4" t="n">
-        <v>77090000</v>
+        <v>105309000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-23442191.4304</v>
+        <v>-2990.183072</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09704400000000001</v>
+        <v>0.000265</v>
       </c>
       <c r="D5" t="n">
-        <v>-81104000</v>
+        <v>-77444000</v>
       </c>
       <c r="E5" t="n">
-        <v>-222589000</v>
+        <v>-11270000</v>
       </c>
       <c r="F5" t="n">
-        <v>-241562000</v>
+        <v>-11270000</v>
       </c>
       <c r="G5" t="n">
-        <v>-260665000</v>
+        <v>-120100000</v>
       </c>
       <c r="H5" t="n">
-        <v>26304000</v>
+        <v>2320000</v>
       </c>
       <c r="I5" t="n">
-        <v>162450000</v>
+        <v>107826000</v>
       </c>
       <c r="J5" t="n">
-        <v>-303693000</v>
+        <v>-88714000</v>
       </c>
       <c r="K5" t="n">
-        <v>-329997000</v>
+        <v>-91034000</v>
       </c>
       <c r="L5" t="n">
-        <v>-78139000</v>
+        <v>-54809000</v>
       </c>
       <c r="M5" t="n">
-        <v>76323000</v>
+        <v>52188000</v>
       </c>
       <c r="N5" t="n">
-        <v>192000</v>
+        <v>4000</v>
       </c>
       <c r="O5" t="n">
-        <v>-23572191.4304</v>
+        <v>-108832990.183072</v>
       </c>
       <c r="P5" t="n">
-        <v>-260665000</v>
+        <v>-120100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>247606000</v>
+        <v>158514000</v>
       </c>
       <c r="R5" t="n">
-        <v>1045740021</v>
+        <v>1966618000</v>
       </c>
       <c r="S5" t="n">
-        <v>1045740021</v>
+        <v>1966618000</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.249627</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.249627</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-260665000</v>
+        <v>-120100000</v>
       </c>
       <c r="W5" t="n">
-        <v>-260665000</v>
+        <v>-120100000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-260665000</v>
+        <v>-120100000</v>
       </c>
       <c r="Z5" t="n">
-        <v>106224000</v>
+        <v>23084000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-366889000</v>
+        <v>-143184000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-366889000</v>
+        <v>-143184000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-39431000</v>
+        <v>-38000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-406320000</v>
+        <v>-143222000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2081000</v>
+        <v>1288000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-195548000</v>
+        <v>-13156000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-80639000</v>
+        <v>-1908000</v>
       </c>
       <c r="AH5" t="n">
-        <v>10889000</v>
+        <v>10953000</v>
       </c>
       <c r="AI5" t="n">
-        <v>246325000</v>
+        <v>4111000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-78139000</v>
+        <v>-54809000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2008000</v>
+        <v>2625000</v>
       </c>
       <c r="AL5" t="n">
-        <v>76323000</v>
+        <v>52188000</v>
       </c>
       <c r="AM5" t="n">
-        <v>192000</v>
+        <v>4000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-88742000</v>
+        <v>-78973000</v>
       </c>
       <c r="AO5" t="n">
-        <v>85156000</v>
+        <v>50688000</v>
       </c>
       <c r="AP5" t="n">
-        <v>86015000</v>
+        <v>55853000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3698000</v>
+        <v>6343000</v>
       </c>
       <c r="AR5" t="n">
-        <v>82317000</v>
+        <v>49510000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-3586000</v>
+        <v>-28285000</v>
       </c>
       <c r="AT5" t="n">
-        <v>162450000</v>
+        <v>107826000</v>
       </c>
       <c r="AU5" t="n">
-        <v>158864000</v>
+        <v>79541000</v>
       </c>
       <c r="AV5" t="n">
-        <v>158864000</v>
+        <v>79541000</v>
       </c>
     </row>
   </sheetData>
@@ -1592,202 +1592,202 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1966618200</v>
+        <v>1045740021</v>
       </c>
       <c r="C2" t="n">
-        <v>1966618200</v>
+        <v>1045740021</v>
       </c>
       <c r="D2" t="n">
-        <v>358518000</v>
+        <v>334566000</v>
       </c>
       <c r="E2" t="n">
-        <v>363628000</v>
+        <v>365653000</v>
       </c>
       <c r="F2" t="n">
-        <v>-436113000</v>
+        <v>-228069000</v>
       </c>
       <c r="G2" t="n">
-        <v>-66876000</v>
+        <v>234809000</v>
       </c>
       <c r="H2" t="n">
-        <v>-776642000</v>
+        <v>-352124000</v>
       </c>
       <c r="I2" t="n">
-        <v>-436113000</v>
+        <v>-228069000</v>
       </c>
       <c r="J2" t="n">
-        <v>540000</v>
+        <v>2046000</v>
       </c>
       <c r="K2" t="n">
-        <v>-429964000</v>
+        <v>-128798000</v>
       </c>
       <c r="L2" t="n">
-        <v>-429964000</v>
+        <v>-26820000</v>
       </c>
       <c r="M2" t="n">
-        <v>-766524000</v>
+        <v>-335282000</v>
       </c>
       <c r="N2" t="n">
-        <v>-336560000</v>
+        <v>-206484000</v>
       </c>
       <c r="O2" t="n">
-        <v>-429964000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>9053000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-2811211000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2193004000</v>
-      </c>
+        <v>-128798000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>17639000</v>
+        <v>870809000</v>
       </c>
       <c r="T2" t="n">
-        <v>17639000</v>
+        <v>870809000</v>
       </c>
       <c r="U2" t="n">
-        <v>848084000</v>
+        <v>733563000</v>
       </c>
       <c r="V2" t="n">
+        <v>112134000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>9091000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>103043000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1065000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>101978000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>621429000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>262610000</v>
+      </c>
+      <c r="AD2" t="n">
         <v>981000</v>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>631000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>350000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>350000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>847103000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>363278000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>190000</v>
-      </c>
       <c r="AE2" t="n">
-        <v>363088000</v>
+        <v>261629000</v>
       </c>
       <c r="AF2" t="n">
-        <v>466215000</v>
+        <v>353786000</v>
       </c>
       <c r="AG2" t="n">
-        <v>427715000</v>
+        <v>266066000</v>
       </c>
       <c r="AH2" t="n">
-        <v>4183000</v>
+        <v>3867000</v>
       </c>
       <c r="AI2" t="n">
-        <v>34317000</v>
+        <v>83853000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>81560000</v>
+        <v>398281000</v>
       </c>
       <c r="AK2" t="n">
-        <v>11099000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>128976000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>4952000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>1447000</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1447000</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>880000</v>
+        <v>1051000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6149000</v>
+        <v>99271000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6149000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>99271000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
       <c r="AS2" t="n">
-        <v>2623000</v>
+        <v>23702000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-359808000</v>
+        <v>-333458000</v>
       </c>
       <c r="AU2" t="n">
-        <v>362431000</v>
+        <v>357160000</v>
       </c>
       <c r="AV2" t="n">
         <v>2417000</v>
       </c>
       <c r="AW2" t="n">
-        <v>214292000</v>
+        <v>210793000</v>
       </c>
       <c r="AX2" t="n">
-        <v>145722000</v>
+        <v>143950000</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>70461000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-371000</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+        <v>269305000</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>58647000</v>
+      </c>
       <c r="BC2" t="n">
-        <v>13947000</v>
+        <v>17806000</v>
       </c>
       <c r="BD2" t="n">
-        <v>28085000</v>
+        <v>43468000</v>
       </c>
       <c r="BE2" t="n">
-        <v>18970000</v>
+        <v>22427000</v>
       </c>
       <c r="BF2" t="n">
-        <v>9115000</v>
+        <v>21041000</v>
       </c>
       <c r="BG2" t="n">
-        <v>9829000</v>
+        <v>42656000</v>
       </c>
       <c r="BH2" t="n">
-        <v>772000</v>
+        <v>258000</v>
       </c>
       <c r="BI2" t="n">
-        <v>13619000</v>
+        <v>46016000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-3976000</v>
+        <v>-22535000</v>
       </c>
       <c r="BK2" t="n">
-        <v>17595000</v>
+        <v>68551000</v>
       </c>
       <c r="BL2" t="n">
-        <v>4580000</v>
+        <v>60454000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10000</v>
+        <v>31413000</v>
       </c>
       <c r="BN2" t="n">
-        <v>4570000</v>
+        <v>29041000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4570000</v>
+        <v>29041000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1151097164</v>
@@ -1796,46 +1796,46 @@
         <v>1151097164</v>
       </c>
       <c r="D3" t="n">
-        <v>341473000</v>
+        <v>340346000</v>
       </c>
       <c r="E3" t="n">
-        <v>356081000</v>
+        <v>344294000</v>
       </c>
       <c r="F3" t="n">
-        <v>-399620000</v>
+        <v>-294392000</v>
       </c>
       <c r="G3" t="n">
-        <v>-34769000</v>
+        <v>93279000</v>
       </c>
       <c r="H3" t="n">
-        <v>-710495000</v>
+        <v>-584137000</v>
       </c>
       <c r="I3" t="n">
-        <v>-399620000</v>
+        <v>-294392000</v>
       </c>
       <c r="J3" t="n">
-        <v>690000</v>
+        <v>394000</v>
       </c>
       <c r="K3" t="n">
-        <v>-390160000</v>
+        <v>-250621000</v>
       </c>
       <c r="L3" t="n">
-        <v>-388610000</v>
+        <v>-245574000</v>
       </c>
       <c r="M3" t="n">
-        <v>-690703000</v>
+        <v>-520226000</v>
       </c>
       <c r="N3" t="n">
-        <v>-300543000</v>
+        <v>-269605000</v>
       </c>
       <c r="O3" t="n">
-        <v>-390160000</v>
+        <v>-250621000</v>
       </c>
       <c r="P3" t="n">
-        <v>2035000</v>
+        <v>7808000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2691537000</v>
+        <v>-2564927000</v>
       </c>
       <c r="R3" t="n">
         <v>1163325000</v>
@@ -1847,140 +1847,144 @@
         <v>956689000</v>
       </c>
       <c r="U3" t="n">
-        <v>817640000</v>
+        <v>694089000</v>
       </c>
       <c r="V3" t="n">
-        <v>2862000</v>
+        <v>7516000</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>799000</v>
+        <v>2195000</v>
       </c>
       <c r="Y3" t="n">
-        <v>2063000</v>
+        <v>5321000</v>
       </c>
       <c r="Z3" t="n">
-        <v>513000</v>
+        <v>274000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1550000</v>
+        <v>5047000</v>
       </c>
       <c r="AB3" t="n">
-        <v>814778000</v>
+        <v>686573000</v>
       </c>
       <c r="AC3" t="n">
-        <v>354018000</v>
+        <v>338973000</v>
       </c>
       <c r="AD3" t="n">
-        <v>177000</v>
+        <v>120000</v>
       </c>
       <c r="AE3" t="n">
-        <v>353841000</v>
+        <v>338853000</v>
       </c>
       <c r="AF3" t="n">
-        <v>453950000</v>
+        <v>341202000</v>
       </c>
       <c r="AG3" t="n">
-        <v>417876000</v>
+        <v>311544000</v>
       </c>
       <c r="AH3" t="n">
-        <v>4120000</v>
+        <v>4137000</v>
       </c>
       <c r="AI3" t="n">
-        <v>31954000</v>
+        <v>25521000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126937000</v>
+        <v>173863000</v>
       </c>
       <c r="AK3" t="n">
-        <v>22654000</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>71427000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
       <c r="AM3" t="n">
-        <v>7108000</v>
+        <v>14052000</v>
       </c>
       <c r="AN3" t="n">
-        <v>7108000</v>
+        <v>14052000</v>
       </c>
       <c r="AO3" t="n">
-        <v>920000</v>
+        <v>1141000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9460000</v>
+        <v>43771000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9460000</v>
+        <v>43771000</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>5166000</v>
+        <v>12463000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-355830000</v>
+        <v>-347276000</v>
       </c>
       <c r="AU3" t="n">
-        <v>360996000</v>
+        <v>359739000</v>
       </c>
       <c r="AV3" t="n">
         <v>2417000</v>
       </c>
       <c r="AW3" t="n">
-        <v>213508000</v>
+        <v>212480000</v>
       </c>
       <c r="AX3" t="n">
-        <v>145071000</v>
+        <v>144842000</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>104283000</v>
+        <v>102436000</v>
       </c>
       <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
       <c r="BC3" t="n">
-        <v>10459000</v>
+        <v>4773000</v>
       </c>
       <c r="BD3" t="n">
-        <v>37970000</v>
+        <v>48749000</v>
       </c>
       <c r="BE3" t="n">
-        <v>33443000</v>
+        <v>31874000</v>
       </c>
       <c r="BF3" t="n">
-        <v>4527000</v>
+        <v>16875000</v>
       </c>
       <c r="BG3" t="n">
-        <v>22322000</v>
+        <v>28164000</v>
       </c>
       <c r="BH3" t="n">
-        <v>55000</v>
+        <v>258000</v>
       </c>
       <c r="BI3" t="n">
-        <v>5551000</v>
+        <v>6812000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-3919000</v>
+        <v>-3843000</v>
       </c>
       <c r="BK3" t="n">
-        <v>9470000</v>
+        <v>10655000</v>
       </c>
       <c r="BL3" t="n">
-        <v>27926000</v>
+        <v>13680000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14008000</v>
+        <v>10126000</v>
       </c>
       <c r="BN3" t="n">
-        <v>13918000</v>
+        <v>3554000</v>
       </c>
       <c r="BO3" t="n">
-        <v>13918000</v>
+        <v>3554000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1151097164</v>
@@ -1989,46 +1993,46 @@
         <v>1151097164</v>
       </c>
       <c r="D4" t="n">
-        <v>340346000</v>
+        <v>341473000</v>
       </c>
       <c r="E4" t="n">
-        <v>344294000</v>
+        <v>356081000</v>
       </c>
       <c r="F4" t="n">
-        <v>-294392000</v>
+        <v>-399620000</v>
       </c>
       <c r="G4" t="n">
-        <v>93279000</v>
+        <v>-34769000</v>
       </c>
       <c r="H4" t="n">
-        <v>-584137000</v>
+        <v>-710495000</v>
       </c>
       <c r="I4" t="n">
-        <v>-294392000</v>
+        <v>-399620000</v>
       </c>
       <c r="J4" t="n">
-        <v>394000</v>
+        <v>690000</v>
       </c>
       <c r="K4" t="n">
-        <v>-250621000</v>
+        <v>-390160000</v>
       </c>
       <c r="L4" t="n">
-        <v>-245574000</v>
+        <v>-388610000</v>
       </c>
       <c r="M4" t="n">
-        <v>-520226000</v>
+        <v>-690703000</v>
       </c>
       <c r="N4" t="n">
-        <v>-269605000</v>
+        <v>-300543000</v>
       </c>
       <c r="O4" t="n">
-        <v>-250621000</v>
+        <v>-390160000</v>
       </c>
       <c r="P4" t="n">
-        <v>7808000</v>
+        <v>2035000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2564927000</v>
+        <v>-2691537000</v>
       </c>
       <c r="R4" t="n">
         <v>1163325000</v>
@@ -2040,334 +2044,330 @@
         <v>956689000</v>
       </c>
       <c r="U4" t="n">
-        <v>694089000</v>
+        <v>817640000</v>
       </c>
       <c r="V4" t="n">
-        <v>7516000</v>
+        <v>2862000</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>2195000</v>
+        <v>799000</v>
       </c>
       <c r="Y4" t="n">
-        <v>5321000</v>
+        <v>2063000</v>
       </c>
       <c r="Z4" t="n">
-        <v>274000</v>
+        <v>513000</v>
       </c>
       <c r="AA4" t="n">
-        <v>5047000</v>
+        <v>1550000</v>
       </c>
       <c r="AB4" t="n">
-        <v>686573000</v>
+        <v>814778000</v>
       </c>
       <c r="AC4" t="n">
-        <v>338973000</v>
+        <v>354018000</v>
       </c>
       <c r="AD4" t="n">
-        <v>120000</v>
+        <v>177000</v>
       </c>
       <c r="AE4" t="n">
-        <v>338853000</v>
+        <v>353841000</v>
       </c>
       <c r="AF4" t="n">
-        <v>341202000</v>
+        <v>453950000</v>
       </c>
       <c r="AG4" t="n">
-        <v>311544000</v>
+        <v>417876000</v>
       </c>
       <c r="AH4" t="n">
-        <v>4137000</v>
+        <v>4120000</v>
       </c>
       <c r="AI4" t="n">
-        <v>25521000</v>
+        <v>31954000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>173863000</v>
+        <v>126937000</v>
       </c>
       <c r="AK4" t="n">
-        <v>71427000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
+        <v>22654000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>14052000</v>
+        <v>7108000</v>
       </c>
       <c r="AN4" t="n">
-        <v>14052000</v>
+        <v>7108000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1141000</v>
+        <v>920000</v>
       </c>
       <c r="AP4" t="n">
-        <v>43771000</v>
+        <v>9460000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>43771000</v>
+        <v>9460000</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>12463000</v>
+        <v>5166000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-347276000</v>
+        <v>-355830000</v>
       </c>
       <c r="AU4" t="n">
-        <v>359739000</v>
+        <v>360996000</v>
       </c>
       <c r="AV4" t="n">
         <v>2417000</v>
       </c>
       <c r="AW4" t="n">
-        <v>212480000</v>
+        <v>213508000</v>
       </c>
       <c r="AX4" t="n">
-        <v>144842000</v>
+        <v>145071000</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>102436000</v>
+        <v>104283000</v>
       </c>
       <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>4773000</v>
+        <v>10459000</v>
       </c>
       <c r="BD4" t="n">
-        <v>48749000</v>
+        <v>37970000</v>
       </c>
       <c r="BE4" t="n">
-        <v>31874000</v>
+        <v>33443000</v>
       </c>
       <c r="BF4" t="n">
-        <v>16875000</v>
+        <v>4527000</v>
       </c>
       <c r="BG4" t="n">
-        <v>28164000</v>
+        <v>22322000</v>
       </c>
       <c r="BH4" t="n">
-        <v>258000</v>
+        <v>55000</v>
       </c>
       <c r="BI4" t="n">
-        <v>6812000</v>
+        <v>5551000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-3843000</v>
+        <v>-3919000</v>
       </c>
       <c r="BK4" t="n">
-        <v>10655000</v>
+        <v>9470000</v>
       </c>
       <c r="BL4" t="n">
-        <v>13680000</v>
+        <v>27926000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10126000</v>
+        <v>14008000</v>
       </c>
       <c r="BN4" t="n">
-        <v>3554000</v>
+        <v>13918000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3554000</v>
+        <v>13918000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1045740021</v>
+        <v>1966618200</v>
       </c>
       <c r="C5" t="n">
-        <v>1045740021</v>
+        <v>1966618200</v>
       </c>
       <c r="D5" t="n">
-        <v>334566000</v>
+        <v>358518000</v>
       </c>
       <c r="E5" t="n">
-        <v>365653000</v>
+        <v>363628000</v>
       </c>
       <c r="F5" t="n">
-        <v>-228069000</v>
+        <v>-436113000</v>
       </c>
       <c r="G5" t="n">
-        <v>234809000</v>
+        <v>-66876000</v>
       </c>
       <c r="H5" t="n">
-        <v>-352124000</v>
+        <v>-776642000</v>
       </c>
       <c r="I5" t="n">
-        <v>-228069000</v>
+        <v>-436113000</v>
       </c>
       <c r="J5" t="n">
-        <v>2046000</v>
+        <v>540000</v>
       </c>
       <c r="K5" t="n">
-        <v>-128798000</v>
+        <v>-429964000</v>
       </c>
       <c r="L5" t="n">
-        <v>-26820000</v>
+        <v>-429964000</v>
       </c>
       <c r="M5" t="n">
-        <v>-335282000</v>
+        <v>-766524000</v>
       </c>
       <c r="N5" t="n">
-        <v>-206484000</v>
+        <v>-336560000</v>
       </c>
       <c r="O5" t="n">
-        <v>-128798000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+        <v>-429964000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>9053000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-2811211000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2193004000</v>
+      </c>
       <c r="S5" t="n">
-        <v>870809000</v>
+        <v>17639000</v>
       </c>
       <c r="T5" t="n">
-        <v>870809000</v>
+        <v>17639000</v>
       </c>
       <c r="U5" t="n">
-        <v>733563000</v>
+        <v>848084000</v>
       </c>
       <c r="V5" t="n">
-        <v>112134000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
+        <v>981000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>9091000</v>
+        <v>631000</v>
       </c>
       <c r="Y5" t="n">
-        <v>103043000</v>
+        <v>350000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1065000</v>
+        <v>350000</v>
       </c>
       <c r="AA5" t="n">
-        <v>101978000</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>621429000</v>
+        <v>847103000</v>
       </c>
       <c r="AC5" t="n">
-        <v>262610000</v>
+        <v>363278000</v>
       </c>
       <c r="AD5" t="n">
-        <v>981000</v>
+        <v>190000</v>
       </c>
       <c r="AE5" t="n">
-        <v>261629000</v>
+        <v>363088000</v>
       </c>
       <c r="AF5" t="n">
-        <v>353786000</v>
+        <v>466215000</v>
       </c>
       <c r="AG5" t="n">
-        <v>266066000</v>
+        <v>427715000</v>
       </c>
       <c r="AH5" t="n">
-        <v>3867000</v>
+        <v>4183000</v>
       </c>
       <c r="AI5" t="n">
-        <v>83853000</v>
+        <v>34317000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>398281000</v>
+        <v>81560000</v>
       </c>
       <c r="AK5" t="n">
-        <v>128976000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>4952000</v>
-      </c>
+        <v>11099000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1447000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1447000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1051000</v>
+        <v>880000</v>
       </c>
       <c r="AP5" t="n">
-        <v>99271000</v>
+        <v>6149000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>99271000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
+        <v>6149000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>23702000</v>
+        <v>2623000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-333458000</v>
+        <v>-359808000</v>
       </c>
       <c r="AU5" t="n">
-        <v>357160000</v>
+        <v>362431000</v>
       </c>
       <c r="AV5" t="n">
         <v>2417000</v>
       </c>
       <c r="AW5" t="n">
-        <v>210793000</v>
+        <v>214292000</v>
       </c>
       <c r="AX5" t="n">
-        <v>143950000</v>
+        <v>145722000</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>269305000</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="n">
-        <v>58647000</v>
-      </c>
+        <v>70461000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-371000</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>17806000</v>
+        <v>13947000</v>
       </c>
       <c r="BD5" t="n">
-        <v>43468000</v>
+        <v>28085000</v>
       </c>
       <c r="BE5" t="n">
-        <v>22427000</v>
+        <v>18970000</v>
       </c>
       <c r="BF5" t="n">
-        <v>21041000</v>
+        <v>9115000</v>
       </c>
       <c r="BG5" t="n">
-        <v>42656000</v>
+        <v>9829000</v>
       </c>
       <c r="BH5" t="n">
-        <v>258000</v>
+        <v>772000</v>
       </c>
       <c r="BI5" t="n">
-        <v>46016000</v>
+        <v>13619000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-22535000</v>
+        <v>-3976000</v>
       </c>
       <c r="BK5" t="n">
-        <v>68551000</v>
+        <v>17595000</v>
       </c>
       <c r="BL5" t="n">
-        <v>60454000</v>
+        <v>4580000</v>
       </c>
       <c r="BM5" t="n">
-        <v>31413000</v>
+        <v>10000</v>
       </c>
       <c r="BN5" t="n">
-        <v>29041000</v>
+        <v>4570000</v>
       </c>
       <c r="BO5" t="n">
-        <v>29041000</v>
+        <v>4570000</v>
       </c>
     </row>
   </sheetData>
@@ -2628,558 +2628,558 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-85374000</v>
+        <v>-20676000</v>
       </c>
       <c r="C2" t="n">
-        <v>-3499000</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>90629000</v>
-      </c>
+        <v>-20900000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>55808000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-59000</v>
+        <v>-18275000</v>
       </c>
       <c r="G2" t="n">
-        <v>4570000</v>
+        <v>29041000</v>
       </c>
       <c r="H2" t="n">
-        <v>13918000</v>
+        <v>46959000</v>
       </c>
       <c r="I2" t="n">
-        <v>2588000</v>
+        <v>-3045000</v>
       </c>
       <c r="J2" t="n">
-        <v>-11936000</v>
+        <v>-14873000</v>
       </c>
       <c r="K2" t="n">
-        <v>62850000</v>
+        <v>3687000</v>
       </c>
       <c r="L2" t="n">
-        <v>-3576000</v>
+        <v>24000</v>
       </c>
       <c r="M2" t="n">
-        <v>-20503000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>90629000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>90629000</v>
-      </c>
+        <v>-30190000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-3499000</v>
+        <v>34908000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3499000</v>
+        <v>34908000</v>
       </c>
       <c r="R2" t="n">
-        <v>-3499000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+        <v>-20900000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>55808000</v>
+      </c>
       <c r="T2" t="n">
-        <v>10529000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>-16159000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>457000</v>
+      </c>
       <c r="V2" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="W2" t="n">
-        <v>16126000</v>
+        <v>3169000</v>
       </c>
       <c r="X2" t="n">
-        <v>16126000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>7334000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-4165000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-1518000</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>-1518000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-4263000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-4263000</v>
+      </c>
       <c r="AE2" t="n">
-        <v>-59000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
+        <v>-14012000</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>-59000</v>
+        <v>-14012000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-85315000</v>
+        <v>-2401000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-100000</v>
+        <v>-1051000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-15912000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>46267000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>12593000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>-29625000</v>
+        <v>43002000</v>
       </c>
       <c r="AM2" t="n">
-        <v>11765000</v>
+        <v>6385000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1948000</v>
+        <v>-15713000</v>
       </c>
       <c r="AO2" t="n">
-        <v>54809000</v>
+        <v>64493000</v>
       </c>
       <c r="AP2" t="n">
-        <v>7444000</v>
+        <v>3768000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2320000</v>
+        <v>26304000</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>9216000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2320000</v>
+        <v>17088000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-1805000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
+        <v>46014000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>-1411000</v>
+        <v>-80639000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-143222000</v>
+        <v>-406320000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-28887000</v>
+        <v>-17586000</v>
       </c>
       <c r="C3" t="n">
-        <v>-2126000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
+        <v>14480000</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-857000</v>
+        <v>-12950000</v>
       </c>
       <c r="G3" t="n">
-        <v>13918000</v>
+        <v>3554000</v>
       </c>
       <c r="H3" t="n">
-        <v>3554000</v>
+        <v>29041000</v>
       </c>
       <c r="I3" t="n">
-        <v>-3305000</v>
+        <v>513000</v>
       </c>
       <c r="J3" t="n">
-        <v>13669000</v>
+        <v>-26000000</v>
       </c>
       <c r="K3" t="n">
-        <v>46828000</v>
+        <v>-7788000</v>
       </c>
       <c r="L3" t="n">
-        <v>49740000</v>
+        <v>-21791000</v>
       </c>
       <c r="M3" t="n">
-        <v>-594000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>-2126000</v>
+        <v>14480000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2126000</v>
+        <v>14480000</v>
       </c>
       <c r="R3" t="n">
-        <v>-2126000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>14480000</v>
       </c>
       <c r="T3" t="n">
-        <v>-5129000</v>
+        <v>-13576000</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="W3" t="n">
-        <v>975000</v>
+        <v>189000</v>
       </c>
       <c r="X3" t="n">
-        <v>975000</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+        <v>189000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
       <c r="Z3" t="n">
-        <v>89000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>89000</v>
-      </c>
+        <v>-819000</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-819000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-12942000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-12942000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-794000</v>
+        <v>-8000</v>
       </c>
       <c r="AF3" t="n">
-        <v>63000</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-857000</v>
+        <v>-8000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-28030000</v>
+        <v>-4636000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-78000</v>
+        <v>-21000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>41119000</v>
+        <v>72783000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>12371000</v>
       </c>
       <c r="AL3" t="n">
-        <v>28450000</v>
+        <v>17985000</v>
       </c>
       <c r="AM3" t="n">
-        <v>10237000</v>
+        <v>-3556000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2432000</v>
+        <v>45983000</v>
       </c>
       <c r="AO3" t="n">
-        <v>70838000</v>
+        <v>75582000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>308000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16646000</v>
+        <v>20934000</v>
       </c>
       <c r="AR3" t="n">
-        <v>10369000</v>
+        <v>13244000</v>
       </c>
       <c r="AS3" t="n">
-        <v>6277000</v>
+        <v>7690000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-4510000</v>
+        <v>20972000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-63000</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>-21760000</v>
+        <v>-27000000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-166001000</v>
+        <v>-220939000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-17586000</v>
+        <v>-28887000</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-2126000</v>
       </c>
       <c r="D4" t="n">
-        <v>14480000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" t="n">
-        <v>-12950000</v>
+        <v>-857000</v>
       </c>
       <c r="G4" t="n">
+        <v>13918000</v>
+      </c>
+      <c r="H4" t="n">
         <v>3554000</v>
       </c>
-      <c r="H4" t="n">
-        <v>29041000</v>
-      </c>
       <c r="I4" t="n">
-        <v>513000</v>
+        <v>-3305000</v>
       </c>
       <c r="J4" t="n">
-        <v>-26000000</v>
+        <v>13669000</v>
       </c>
       <c r="K4" t="n">
-        <v>-7788000</v>
+        <v>46828000</v>
       </c>
       <c r="L4" t="n">
-        <v>-21791000</v>
+        <v>49740000</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+        <v>-594000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>14480000</v>
+        <v>-2126000</v>
       </c>
       <c r="Q4" t="n">
-        <v>14480000</v>
+        <v>-2126000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-2126000</v>
       </c>
       <c r="S4" t="n">
-        <v>14480000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-13576000</v>
+        <v>-5129000</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="W4" t="n">
-        <v>189000</v>
+        <v>975000</v>
       </c>
       <c r="X4" t="n">
-        <v>189000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
+        <v>975000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-819000</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+        <v>89000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>89000</v>
+      </c>
       <c r="AB4" t="n">
-        <v>-819000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-12942000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-12942000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-8000</v>
+        <v>-794000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-8000</v>
+        <v>-857000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-4636000</v>
+        <v>-28030000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-21000</v>
+        <v>-78000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>72783000</v>
+        <v>41119000</v>
       </c>
       <c r="AK4" t="n">
-        <v>12371000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>17985000</v>
+        <v>28450000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-3556000</v>
+        <v>10237000</v>
       </c>
       <c r="AN4" t="n">
-        <v>45983000</v>
+        <v>2432000</v>
       </c>
       <c r="AO4" t="n">
-        <v>75582000</v>
+        <v>70838000</v>
       </c>
       <c r="AP4" t="n">
-        <v>308000</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20934000</v>
+        <v>16646000</v>
       </c>
       <c r="AR4" t="n">
-        <v>13244000</v>
+        <v>10369000</v>
       </c>
       <c r="AS4" t="n">
-        <v>7690000</v>
+        <v>6277000</v>
       </c>
       <c r="AT4" t="n">
-        <v>20972000</v>
+        <v>-4510000</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>-63000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-27000000</v>
+        <v>-21760000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-220939000</v>
+        <v>-166001000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-20676000</v>
+        <v>-85374000</v>
       </c>
       <c r="C5" t="n">
-        <v>-20900000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>55808000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>-3499000</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>90629000</v>
+      </c>
       <c r="F5" t="n">
-        <v>-18275000</v>
+        <v>-59000</v>
       </c>
       <c r="G5" t="n">
-        <v>29041000</v>
+        <v>4570000</v>
       </c>
       <c r="H5" t="n">
-        <v>46959000</v>
+        <v>13918000</v>
       </c>
       <c r="I5" t="n">
-        <v>-3045000</v>
+        <v>2588000</v>
       </c>
       <c r="J5" t="n">
-        <v>-14873000</v>
+        <v>-11936000</v>
       </c>
       <c r="K5" t="n">
-        <v>3687000</v>
+        <v>62850000</v>
       </c>
       <c r="L5" t="n">
-        <v>24000</v>
+        <v>-3576000</v>
       </c>
       <c r="M5" t="n">
-        <v>-30190000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>-20503000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>90629000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>90629000</v>
+      </c>
       <c r="P5" t="n">
-        <v>34908000</v>
+        <v>-3499000</v>
       </c>
       <c r="Q5" t="n">
-        <v>34908000</v>
+        <v>-3499000</v>
       </c>
       <c r="R5" t="n">
-        <v>-20900000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>55808000</v>
-      </c>
+        <v>-3499000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-16159000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>457000</v>
-      </c>
+        <v>10529000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="W5" t="n">
-        <v>3169000</v>
+        <v>16126000</v>
       </c>
       <c r="X5" t="n">
-        <v>7334000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-4165000</v>
-      </c>
+        <v>16126000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-1518000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
-      <c r="AB5" t="n">
-        <v>-1518000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-4263000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-4263000</v>
-      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-14012000</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>-59000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
       <c r="AG5" t="n">
-        <v>-14012000</v>
+        <v>-59000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2401000</v>
+        <v>-85315000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1051000</v>
+        <v>-100000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>46267000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>12593000</v>
-      </c>
+        <v>-15912000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>43002000</v>
+        <v>-29625000</v>
       </c>
       <c r="AM5" t="n">
-        <v>6385000</v>
+        <v>11765000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-15713000</v>
+        <v>1948000</v>
       </c>
       <c r="AO5" t="n">
-        <v>64493000</v>
+        <v>54809000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3768000</v>
+        <v>7444000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26304000</v>
+        <v>2320000</v>
       </c>
       <c r="AR5" t="n">
-        <v>9216000</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>17088000</v>
+        <v>2320000</v>
       </c>
       <c r="AT5" t="n">
-        <v>46014000</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+        <v>-1805000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
       <c r="AV5" t="n">
-        <v>-80639000</v>
+        <v>-1411000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-406320000</v>
+        <v>-143222000</v>
       </c>
     </row>
   </sheetData>
@@ -3704,92 +3704,92 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="DP1" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Zhiqiang  Lu', 'age': 50, 'title': 'Chairman of the Board', 'yearBorn': 1975, 'fiscalYear': 2024, 'totalPay': 61382, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wei Ping  Leong', 'age': 44, 'title': 'Executive Director', 'yearBorn': 1981, 'fiscalYear': 2024, 'totalPay': 640452, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Po Yi  Tang', 'age': 32, 'title': 'Executive Director', 'yearBorn': 1993, 'fiscalYear': 2024, 'totalPay': 907983, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Minbin  Liu', 'age': 62, 'title': 'Executive Director', 'yearBorn': 1963, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Mengling  Zha', 'age': 34, 'title': 'Executive Director', 'yearBorn': 1991, 'fiscalYear': 2024, 'totalPay': 513057, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yang  Li', 'age': 53, 'title': 'Executive Director', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 163298, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kwok Fat  Li A.C.I.S., A.C.S., C.P.A.', 'age': 49, 'title': 'Chief Financial Officer', 'yearBorn': 1976, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Siu Hung  Sze', 'age': 60, 'title': 'Managing Director', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wing Shan  Ling Law', 'age': 46, 'title': 'Company Secretary', 'yearBorn': 1979, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Zhiqiang  Lu', 'age': 50, 'title': 'Chairman of the Board', 'yearBorn': 1975, 'fiscalYear': 2024, 'totalPay': 61348, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wei Ping  Leong', 'age': 44, 'title': 'Executive Director', 'yearBorn': 1981, 'fiscalYear': 2024, 'totalPay': 640108, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Po Yi  Tang', 'age': 32, 'title': 'Executive Director', 'yearBorn': 1993, 'fiscalYear': 2024, 'totalPay': 907494, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Minbin  Liu', 'age': 62, 'title': 'Executive Director', 'yearBorn': 1963, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Mengling  Zha', 'age': 34, 'title': 'Executive Director', 'yearBorn': 1991, 'fiscalYear': 2024, 'totalPay': 512781, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yang  Li', 'age': 53, 'title': 'Executive Director', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 163210, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kwok Fat  Li A.C.I.S., A.C.S., C.P.A.', 'age': 49, 'title': 'Chief Financial Officer', 'yearBorn': 1976, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Siu Hung  Sze', 'age': 60, 'title': 'Managing Director', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wing Shan  Ling Law', 'age': 46, 'title': 'Company Secretary', 'yearBorn': 1979, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4022,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.003</v>
+        <v>0.996</v>
       </c>
       <c r="AF2" t="n">
         <v>1208000</v>
@@ -4061,7 +4061,7 @@
         <v>0.055</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.08</v>
+        <v>0.073</v>
       </c>
       <c r="AS2" t="n">
         <v>15.8</v>
@@ -4114,7 +4114,7 @@
         <v>2228826200</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0.25363305</v>
+        <v>-0.25349647</v>
       </c>
       <c r="BJ2" t="n">
         <v>1735603200</v>
@@ -4146,10 +4146,10 @@
         <v>-1.62</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.11764705</v>
+        <v>-0.0625</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="n">
         <v>0.094915</v>
@@ -4258,75 +4258,75 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
+          <t>ATV HOLDINGS</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>Asia Television Holdings Limited</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>1754630967</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>finmb_26446900</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>5.2631555</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
           <t>PREPRE</t>
         </is>
       </c>
-      <c r="CY2" t="n">
-        <v>5.2631555</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>Asia Television Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>-0.23656222</v>
-      </c>
-      <c r="DC2" t="n">
+      <c r="DL2" t="n">
+        <v>-0.23668969</v>
+      </c>
+      <c r="DM2" t="n">
         <v>15</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DN2" t="n">
         <v>15</v>
       </c>
-      <c r="DE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>1754630967</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>finmb_26446900</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>ATV HOLDINGS</t>
-        </is>
+      <c r="DO2" t="b">
+        <v>0</v>
       </c>
       <c r="DP2" t="b">
         <v>0</v>
@@ -4358,17 +4358,17 @@
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>0.055 - 0.08</t>
+          <t>0.055 - 0.073</t>
         </is>
       </c>
       <c r="DY2" t="n">
-        <v>-0.02</v>
+        <v>-0.013</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.25</v>
+        <v>-0.1780822</v>
       </c>
       <c r="EA2" t="n">
-        <v>-11.764706</v>
+        <v>-6.25</v>
       </c>
       <c r="EB2" t="n">
         <v>1756377614</v>
